--- a/data/trans_camb/IP04F-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Habitat-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 6,46</t>
+          <t>-3,61; 6,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 2,82</t>
+          <t>-7,13; 3,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,61</t>
+          <t>-3,67; 3,18</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 151,47</t>
+          <t>-40,49; 188,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,99; 62,85</t>
+          <t>-68,72; 63,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 69,53</t>
+          <t>-41,15; 60,23</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 1,02</t>
+          <t>-7,1; 0,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 4,16</t>
+          <t>-4,1; 4,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 1,58</t>
+          <t>-4,48; 1,31</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,34; 13,28</t>
+          <t>-58,16; 14,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 70,48</t>
+          <t>-41,43; 75,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 23,03</t>
+          <t>-42,59; 18,29</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 1,71</t>
+          <t>-8,0; 1,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 3,59</t>
+          <t>-8,0; 3,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,97</t>
+          <t>-6,42; 0,87</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,61; 26,14</t>
+          <t>-63,34; 22,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,59; 46,01</t>
+          <t>-56,24; 40,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 11,33</t>
+          <t>-49,53; 11,64</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 5,14</t>
+          <t>-6,15; 5,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 3,09</t>
+          <t>-6,22; 3,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 2,68</t>
+          <t>-4,61; 2,46</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 46,7</t>
+          <t>-37,95; 48,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 43,4</t>
+          <t>-50,73; 45,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 28,69</t>
+          <t>-34,7; 25,73</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,06</t>
+          <t>-4,06; 1,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,17</t>
+          <t>-3,59; 1,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,63</t>
+          <t>-3,11; 0,31</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 11,47</t>
+          <t>-34,4; 11,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 14,4</t>
+          <t>-35,94; 17,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 7,46</t>
+          <t>-29,22; 3,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04F-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Habitat-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 6,69</t>
+          <t>-3,51; 7,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 3,01</t>
+          <t>-6,35; 2,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,18</t>
+          <t>-3,65; 3,32</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 188,77</t>
+          <t>-40,47; 206,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-68,72; 63,98</t>
+          <t>-63,58; 59,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 60,23</t>
+          <t>-41,48; 65,66</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 0,92</t>
+          <t>-7,42; 0,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 4,42</t>
+          <t>-4,15; 4,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 1,31</t>
+          <t>-4,72; 1,42</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 14,8</t>
+          <t>-59,23; 14,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,43; 75,35</t>
+          <t>-41,44; 72,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,59; 18,29</t>
+          <t>-43,26; 21,5</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 1,28</t>
+          <t>-8,18; 2,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 3,27</t>
+          <t>-7,66; 2,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 0,87</t>
+          <t>-6,41; 0,85</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,34; 22,03</t>
+          <t>-65,5; 28,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,24; 40,9</t>
+          <t>-56,39; 34,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 11,64</t>
+          <t>-49,93; 9,85</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 5,3</t>
+          <t>-6,34; 5,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 3,03</t>
+          <t>-5,71; 3,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 2,46</t>
+          <t>-4,53; 2,49</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 48,59</t>
+          <t>-38,12; 52,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 45,36</t>
+          <t>-50,92; 48,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 25,73</t>
+          <t>-34,31; 25,74</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,02</t>
+          <t>-4,24; 1,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,26</t>
+          <t>-3,61; 1,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,31</t>
+          <t>-3,1; 0,44</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 11,24</t>
+          <t>-35,13; 11,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 17,2</t>
+          <t>-35,0; 14,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 3,48</t>
+          <t>-29,73; 5,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04F-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Habitat-trans_camb.xlsx
@@ -495,12 +495,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1,44</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,77</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 7,02</t>
+          <t>-6,26; 2,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 2,93</t>
+          <t>-4,0; 6,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,32</t>
+          <t>-3,7; 3,61</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-23,27%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>22,04%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-23,27%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 206,37</t>
+          <t>-63,99; 62,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,58; 59,23</t>
+          <t>-44,77; 151,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,48; 65,66</t>
+          <t>-42,26; 69,53</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>-3,09</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 0,98</t>
+          <t>-3,97; 4,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 4,31</t>
+          <t>-7,52; 1,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 1,42</t>
+          <t>-4,49; 1,58</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>-31,06%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,23; 14,17</t>
+          <t>-41,99; 70,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,44; 72,94</t>
+          <t>-61,34; 13,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 21,5</t>
+          <t>-42,41; 23,03</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>-3,03</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,22</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 2,0</t>
+          <t>-7,44; 3,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 2,7</t>
+          <t>-8,21; 1,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 0,85</t>
+          <t>-6,23; 0,97</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-20,12%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>-30,57%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-20,12%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,5; 28,55</t>
+          <t>-52,59; 46,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,39; 34,18</t>
+          <t>-62,61; 26,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 9,85</t>
+          <t>-50,66; 11,33</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>-0,71</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-1,28</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 5,3</t>
+          <t>-5,76; 3,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 3,21</t>
+          <t>-6,6; 5,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 2,49</t>
+          <t>-4,41; 2,68</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-13,72%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>-5,18%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-13,72%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 52,25</t>
+          <t>-48,45; 43,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,92; 48,45</t>
+          <t>-38,99; 46,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 25,74</t>
+          <t>-33,29; 28,69</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>-1,49</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,01</t>
+          <t>-3,65; 1,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,13</t>
+          <t>-4,02; 1,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,44</t>
+          <t>-3,09; 0,63</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-12,97%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>-14,31%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-12,97%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 11,42</t>
+          <t>-35,43; 14,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 14,91</t>
+          <t>-34,82; 11,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 5,29</t>
+          <t>-29,15; 7,46</t>
         </is>
       </c>
     </row>
